--- a/v3/OG0060/OG0060_ReadingQuiz.xlsx
+++ b/v3/OG0060/OG0060_ReadingQuiz.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUIZ_LIST" sheetId="1" r:id="R739f1af5886e48f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUESTIONS" sheetId="2" r:id="R8626b1a3523148d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANSWER_SCORING" sheetId="3" r:id="Rdc0f4557fd1c4fe7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FEEDBACK" sheetId="4" r:id="Rd792939dcea84c87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUIZ_LIST" sheetId="1" r:id="R3b446f0499354f28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUESTIONS" sheetId="2" r:id="Rec19ed043f9a4a15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANSWER_SCORING" sheetId="3" r:id="R6d02979ef4da46b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FEEDBACK" sheetId="4" r:id="Rd8c3cec83aa74447"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -643,7 +643,7 @@
         <x:v>Connect</x:v>
       </x:c>
       <x:c r="H11" s="20" t="str">
-        <x:v>Listen for how Pip feels before he makes a little house.</x:v>
+        <x:v>Listen for how Pip feels now.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -943,7 +943,7 @@
         <x:v>Listen. Which scene starts Pip's big change?</x:v>
       </x:c>
       <x:c r="H7" s="20" t="str">
-        <x:v>Listen for how Pip feels before he makes a little house.</x:v>
+        <x:v>Listen for how Pip feels now.</x:v>
       </x:c>
       <x:c r="I7" s="20" t="str">
         <x:v>SC08</x:v>
@@ -1075,7 +1075,7 @@
       </x:c>
       <x:c r="J10" s="20" t="str">
         <x:v>A. Now I will wait for Dot. [100]
-B. Dot will change too. [67]
+B. Dot will not change. [0]
 C. I want more leaves. [33]
 D. I do not need Dot. [0]</x:v>
       </x:c>
@@ -1926,37 +1926,37 @@
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="31" t="str">
+      <x:c r="A26" s="35" t="str">
         <x:v>Q6</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="str">
+      <x:c r="B26" s="35" t="str">
         <x:v>internal_response</x:v>
       </x:c>
-      <x:c r="C26" s="31" t="str">
+      <x:c r="C26" s="35" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="str">
-        <x:v>Dot will change too.</x:v>
-      </x:c>
-      <x:c r="E26" s="31" t="str">
+      <x:c r="D26" s="35" t="str">
+        <x:v>Dot will not change.</x:v>
+      </x:c>
+      <x:c r="E26" s="35" t="str">
         <x:v>Distractor</x:v>
       </x:c>
-      <x:c r="F26" s="32" t="str">
-        <x:v>Partial</x:v>
-      </x:c>
-      <x:c r="G26" s="32" t="n">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="H26" s="31" t="str">
-        <x:v>partial_internal_inference</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="str">
-        <x:v>Dot의 다음 변화를 예상하지만 Pip이 친구를 위해 하려는 행동까지 연결하지 못합니다.</x:v>
-      </x:c>
-      <x:c r="J26" s="31" t="str">
-        <x:v>핵심 생각은 잡았으므로 장면 근거와 더 정확히 연결합니다.</x:v>
-      </x:c>
-      <x:c r="K26" s="31" t="str">
+      <x:c r="F26" s="36" t="str">
+        <x:v>Unrelated</x:v>
+      </x:c>
+      <x:c r="G26" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H26" s="35" t="str">
+        <x:v>opposite_or_no_inference</x:v>
+      </x:c>
+      <x:c r="I26" s="35" t="str">
+        <x:v>Dot의 변화 가능성과 Pip이 기다리려는 이유를 반대로 이해합니다.</x:v>
+      </x:c>
+      <x:c r="J26" s="35" t="str">
+        <x:v>결말 장면을 다시 읽고 인물이 이전과 달라진 점부터 찾습니다.</x:v>
+      </x:c>
+      <x:c r="K26" s="35" t="str">
         <x:v>Character State, Motivation, Inference</x:v>
       </x:c>
     </x:row>
